--- a/Oklahoma_City_Thunder_2025-26_stats.xlsx
+++ b/Oklahoma_City_Thunder_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,6 +1218,60 @@
       </c>
       <c r="P14" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2016,6 +2070,60 @@
       </c>
       <c r="P14" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2029,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2814,6 +2922,60 @@
       </c>
       <c r="P14" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2827,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3611,6 +3773,60 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3647,7 +3863,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32.53846153846154</v>
+        <v>32.57142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -3657,7 +3873,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.66666666666667</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="4">
@@ -3667,7 +3883,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.92307692307692</v>
+        <v>16.71428571428572</v>
       </c>
     </row>
     <row r="5">
@@ -3677,7 +3893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.25</v>
+        <v>14.77777777777778</v>
       </c>
     </row>
     <row r="6">
@@ -3697,7 +3913,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.76923076923077</v>
+        <v>12.71428571428571</v>
       </c>
     </row>
     <row r="8">
@@ -3707,7 +3923,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.416666666666666</v>
+        <v>8.538461538461538</v>
       </c>
     </row>
     <row r="9">
@@ -3717,7 +3933,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.142857142857143</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="10">
@@ -3727,7 +3943,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.444444444444445</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="11">
@@ -3743,41 +3959,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Branden Carlson</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7</v>
+        <v>2.777777777777778</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Branden Carlson</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.25</v>
+        <v>2.636363636363636</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brooks Barnhizer</t>
+          <t>Chris Youngblood</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.272727272727273</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chris Youngblood</t>
+          <t>Brooks Barnhizer</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.25</v>
+        <v>1.166666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -3813,7 +4029,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.615384615384615</v>
+        <v>6.642857142857143</v>
       </c>
     </row>
     <row r="3">
@@ -3823,7 +4039,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.846153846153846</v>
+        <v>3.857142857142857</v>
       </c>
     </row>
     <row r="4">
@@ -3833,27 +4049,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.923076923076923</v>
+        <v>3.071428571428572</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.666666666666667</v>
+        <v>2.769230769230769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.666666666666667</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -3883,7 +4099,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.777777777777778</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="10">
@@ -3893,7 +4109,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.571428571428571</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -3903,7 +4119,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.375</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3913,7 +4129,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="13">
@@ -3923,7 +4139,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.375</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -3933,7 +4149,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -3979,7 +4195,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.15384615384615</v>
+        <v>11.21428571428571</v>
       </c>
     </row>
     <row r="3">
@@ -3989,7 +4205,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.222222222222221</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3999,7 +4215,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.153846153846154</v>
+        <v>5.071428571428571</v>
       </c>
     </row>
     <row r="5">
@@ -4009,7 +4225,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4.875</v>
       </c>
     </row>
     <row r="6">
@@ -4029,7 +4245,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.846153846153846</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -4045,21 +4261,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.25</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.125</v>
+        <v>3.153846153846154</v>
       </c>
     </row>
     <row r="11">
@@ -4069,37 +4285,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.333333333333333</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Brooks Barnhizer</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9</v>
+        <v>2.083333333333333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Branden Carlson</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.875</v>
+        <v>1.909090909090909</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brooks Barnhizer</t>
+          <t>Branden Carlson</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.818181818181818</v>
+        <v>1.888888888888889</v>
       </c>
     </row>
     <row r="15">
@@ -4145,7 +4361,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.625</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -4165,7 +4381,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.153846153846154</v>
+        <v>2.214285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -4175,7 +4391,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.583333333333333</v>
+        <v>1.615384615384615</v>
       </c>
     </row>
     <row r="6">
@@ -4185,27 +4401,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.555555555555556</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Jaylin Williams</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.444444444444444</v>
+        <v>1.307692307692308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jaylin Williams</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.307692307692308</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
@@ -4215,7 +4431,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.307692307692308</v>
+        <v>1.285714285714286</v>
       </c>
     </row>
     <row r="10">
@@ -4231,27 +4447,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ousmane Dieng</t>
+          <t>Branden Carlson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chris Youngblood</t>
+          <t>Ousmane Dieng</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.25</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Branden Carlson</t>
+          <t>Chris Youngblood</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4289,7 +4505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4592,6 +4808,27 @@
         <v>213</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>109</v>
+      </c>
+      <c r="D15" t="n">
+        <v>96</v>
+      </c>
+      <c r="E15" t="n">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
